--- a/StructureDefinition-inera-ehds-imaging-study.xlsx
+++ b/StructureDefinition-inera-ehds-imaging-study.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -680,7 +680,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/imaging-study-status-uv-ips</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/imaging-study-status-uv-ips|2.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1057,7 +1057,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.1}
 </t>
   </si>
   <si>

--- a/StructureDefinition-inera-ehds-imaging-study.xlsx
+++ b/StructureDefinition-inera-ehds-imaging-study.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-imaging-study.xlsx
+++ b/StructureDefinition-inera-ehds-imaging-study.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-imaging-study.xlsx
+++ b/StructureDefinition-inera-ehds-imaging-study.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -426,7 +426,7 @@
 </t>
   </si>
   <si>
-    <t>Källsystem HSA-id (imagingOutcomeHeader.sourceSystemHSAId)</t>
+    <t>Källsystem HSA-id (imagingOutcomeHeader.sourceSystemHSAId) – https://tjanstekatalogen.inera.se/Endpoint/{hsaId} (GENERAL-005)</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -680,7 +680,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/imaging-study-status-uv-ips|2.0.1</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/imaging-study-status-uv-ips</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1057,7 +1057,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.1}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
 </t>
   </si>
   <si>
